--- a/outputs/TAS_mlf.xlsx
+++ b/outputs/TAS_mlf.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1279,12 +1279,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>TRIBNL1</t>
+          <t>JBUTTERS</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Tribute Power Station</t>
+          <t>John Butters Power Station</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1293,52 +1293,52 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>25</v>
+        <v>144</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.9641999999999999</v>
+        <v>0.9384</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.971</v>
+        <v>0.9456</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.9607</v>
+        <v>0.9445</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.9552</v>
+        <v>0.9365</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.9611</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.9454</v>
+        <v>0.923</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.9369</v>
+        <v>0.9258</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0.9582000000000001</v>
+        <v>0.9395</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0.9373</v>
+        <v>0.9208</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>0.9542</v>
+        <v>0.9245</v>
       </c>
       <c r="O12" s="5" t="inlineStr"/>
       <c r="P12" s="5" t="n">
-        <v>0.9586</v>
+        <v>0.9386</v>
       </c>
       <c r="Q12" s="5" t="inlineStr"/>
       <c r="R12" s="5" t="n">
-        <v>0.9586</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="S12" s="5" t="inlineStr"/>
       <c r="T12" s="5" t="n">
-        <v>0</v>
+        <v>0.0216</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V12" s="5" t="inlineStr"/>
       <c r="W12" s="6" t="inlineStr"/>
@@ -1346,12 +1346,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>JBUTTERS</t>
+          <t>BASTYAN</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>John Butters Power Station</t>
+          <t>Bastyan Power Station</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1360,52 +1360,52 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>144</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.9384</v>
+        <v>0.9466</v>
       </c>
       <c r="F13" s="5" t="n">
+        <v>0.9496</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.9486</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="I13" s="5" t="n">
         <v>0.9456</v>
       </c>
-      <c r="G13" s="5" t="n">
-        <v>0.9445</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>0.9365</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>0.9370000000000001</v>
-      </c>
       <c r="J13" s="5" t="n">
-        <v>0.923</v>
+        <v>0.9301</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.9258</v>
+        <v>0.9286</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>0.9395</v>
+        <v>0.9334</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>0.9208</v>
+        <v>0.9202</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>0.9245</v>
+        <v>0.9313</v>
       </c>
       <c r="O13" s="5" t="inlineStr"/>
       <c r="P13" s="5" t="n">
-        <v>0.9386</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="Q13" s="5" t="inlineStr"/>
       <c r="R13" s="5" t="n">
-        <v>0.9602000000000001</v>
+        <v>0.9623</v>
       </c>
       <c r="S13" s="5" t="inlineStr"/>
       <c r="T13" s="5" t="n">
-        <v>0.0216</v>
+        <v>0.0283</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>2.3</v>
+        <v>3.03</v>
       </c>
       <c r="V13" s="5" t="inlineStr"/>
       <c r="W13" s="6" t="inlineStr"/>
@@ -1413,66 +1413,58 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>BASTYAN</t>
+          <t>GRANWF1</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Bastyan Power Station</t>
+          <t>Granville Harbour Wind Farm</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>79.90000000000001</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>0.9466</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>0.9496</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>0.9486</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>0.9409999999999999</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="n">
-        <v>0.9456</v>
+        <v>0.959</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.9301</v>
+        <v>0.9408</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.9286</v>
+        <v>0.9314</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>0.9334</v>
+        <v>0.9543</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0.9202</v>
+        <v>0.9388</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>0.9313</v>
+        <v>0.9473</v>
       </c>
       <c r="O14" s="5" t="inlineStr"/>
       <c r="P14" s="5" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9555</v>
       </c>
       <c r="Q14" s="5" t="inlineStr"/>
       <c r="R14" s="5" t="n">
-        <v>0.9623</v>
+        <v>0.9688</v>
       </c>
       <c r="S14" s="5" t="inlineStr"/>
       <c r="T14" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.0133</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>3.03</v>
+        <v>1.39</v>
       </c>
       <c r="V14" s="5" t="inlineStr"/>
       <c r="W14" s="6" t="inlineStr"/>
@@ -1480,58 +1472,66 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>GRANWF1</t>
+          <t>CETHANA</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Granville Harbour Wind Farm</t>
+          <t>Cethana Power Station</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>110</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9671</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.9723000000000001</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>0.9628</v>
+      </c>
       <c r="I15" s="5" t="n">
-        <v>0.959</v>
+        <v>0.9658</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.9408</v>
+        <v>0.9545</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.9314</v>
+        <v>0.9512</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>0.9543</v>
+        <v>0.9544</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>0.9388</v>
+        <v>0.9504</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>0.9473</v>
+        <v>0.958</v>
       </c>
       <c r="O15" s="5" t="inlineStr"/>
       <c r="P15" s="5" t="n">
-        <v>0.9555</v>
+        <v>0.9473</v>
       </c>
       <c r="Q15" s="5" t="inlineStr"/>
       <c r="R15" s="5" t="n">
-        <v>0.9688</v>
+        <v>0.9705</v>
       </c>
       <c r="S15" s="5" t="inlineStr"/>
       <c r="T15" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0232</v>
       </c>
       <c r="U15" s="6" t="n">
-        <v>1.39</v>
+        <v>2.45</v>
       </c>
       <c r="V15" s="5" t="inlineStr"/>
       <c r="W15" s="6" t="inlineStr"/>
@@ -1539,12 +1539,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>CETHANA</t>
+          <t>DEVILS_G</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Cethana Power Station</t>
+          <t>Devils Gate Power Station</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1553,52 +1553,52 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.9671</v>
+        <v>0.9719</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.963</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="H16" s="5" t="n">
+        <v>0.9692</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>0.9698</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>0.9618</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0.9566</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>0.9594</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>0.9537</v>
+      </c>
+      <c r="N16" s="5" t="n">
         <v>0.9628</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>0.9658</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>0.9545</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>0.9512</v>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>0.9544</v>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v>0.9504</v>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v>0.958</v>
       </c>
       <c r="O16" s="5" t="inlineStr"/>
       <c r="P16" s="5" t="n">
-        <v>0.9473</v>
+        <v>0.9616</v>
       </c>
       <c r="Q16" s="5" t="inlineStr"/>
       <c r="R16" s="5" t="n">
-        <v>0.9705</v>
+        <v>0.9761</v>
       </c>
       <c r="S16" s="5" t="inlineStr"/>
       <c r="T16" s="5" t="n">
-        <v>0.0232</v>
+        <v>0.0145</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>2.45</v>
+        <v>1.51</v>
       </c>
       <c r="V16" s="5" t="inlineStr"/>
       <c r="W16" s="6" t="inlineStr"/>
@@ -1606,12 +1606,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>DEVILS_G</t>
+          <t>TRIBNL1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Devils Gate Power Station</t>
+          <t>Tribute Power Station</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1620,52 +1620,52 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.9719</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.97</v>
+        <v>0.971</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.9607</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.9692</v>
+        <v>0.9552</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.9698</v>
+        <v>0.9611</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.9618</v>
+        <v>0.9454</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.9566</v>
+        <v>0.9369</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.9594</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>0.9537</v>
+        <v>0.9373</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0.9628</v>
+        <v>0.9542</v>
       </c>
       <c r="O17" s="5" t="inlineStr"/>
       <c r="P17" s="5" t="n">
-        <v>0.9616</v>
+        <v>0.9586</v>
       </c>
       <c r="Q17" s="5" t="inlineStr"/>
       <c r="R17" s="5" t="n">
-        <v>0.9761</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="S17" s="5" t="inlineStr"/>
       <c r="T17" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0207</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>1.51</v>
+        <v>2.16</v>
       </c>
       <c r="V17" s="5" t="inlineStr"/>
       <c r="W17" s="6" t="inlineStr"/>
@@ -1941,12 +1941,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>POAT110</t>
+          <t>GORDON</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Poatina Power Station</t>
+          <t>Gordon Power Station</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1955,41 +1955,41 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>100</v>
+        <v>432</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.963</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9676</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.9677</v>
+        <v>0.9594</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>0.9799</v>
+        <v>0.9868</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.9728</v>
+        <v>0.9594</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.9512</v>
+        <v>0.928</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>0.9625</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>0.9555</v>
+        <v>0.9731</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>0.9641</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="O22" s="5" t="inlineStr"/>
       <c r="P22" s="5" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.9594</v>
       </c>
       <c r="Q22" s="5" t="inlineStr"/>
       <c r="R22" s="5" t="n">
@@ -1997,10 +1997,10 @@
       </c>
       <c r="S22" s="5" t="inlineStr"/>
       <c r="T22" s="5" t="n">
-        <v>0.0109</v>
+        <v>0.0278</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>1.12</v>
+        <v>2.9</v>
       </c>
       <c r="V22" s="5" t="inlineStr"/>
       <c r="W22" s="6" t="inlineStr"/>
@@ -2008,12 +2008,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GORDON</t>
+          <t>POAT110</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Gordon Power Station</t>
+          <t>Poatina Power Station</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2022,41 +2022,41 @@
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>432</v>
+        <v>100</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.963</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.9676</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.9594</v>
+        <v>0.9677</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>0.9868</v>
+        <v>0.9799</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0.9594</v>
+        <v>0.9728</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0.928</v>
+        <v>0.9512</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9625</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>0.9731</v>
+        <v>0.9555</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9641</v>
       </c>
       <c r="O23" s="5" t="inlineStr"/>
       <c r="P23" s="5" t="n">
-        <v>0.9594</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="Q23" s="5" t="inlineStr"/>
       <c r="R23" s="5" t="n">
@@ -2064,10 +2064,10 @@
       </c>
       <c r="S23" s="5" t="inlineStr"/>
       <c r="T23" s="5" t="n">
-        <v>0.0278</v>
+        <v>0.0109</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>2.9</v>
+        <v>1.12</v>
       </c>
       <c r="V23" s="5" t="inlineStr"/>
       <c r="W23" s="6" t="inlineStr"/>
@@ -2075,12 +2075,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>PO110NL1</t>
+          <t>TREVALLN</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Poatina Power Station</t>
+          <t>Trevallyn Power Station</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -2089,52 +2089,52 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.9911</v>
+        <v>0.9857</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>1.0012</v>
+        <v>0.9927</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.9937</v>
+        <v>0.9898</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0.9943</v>
+        <v>0.9909</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0.9902</v>
+        <v>0.9889</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.9805</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0.9815</v>
+        <v>0.9848</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0.9774</v>
+        <v>0.9891</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0.9726</v>
+        <v>0.9825</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>0.9846</v>
+        <v>0.99</v>
       </c>
       <c r="O24" s="5" t="inlineStr"/>
       <c r="P24" s="5" t="n">
-        <v>0.9891</v>
+        <v>0.9852</v>
       </c>
       <c r="Q24" s="5" t="inlineStr"/>
       <c r="R24" s="5" t="n">
-        <v>0.9891</v>
+        <v>0.997</v>
       </c>
       <c r="S24" s="5" t="inlineStr"/>
       <c r="T24" s="5" t="n">
-        <v>0</v>
+        <v>0.0118</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V24" s="5" t="inlineStr"/>
       <c r="W24" s="6" t="inlineStr"/>
@@ -2142,12 +2142,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>GOVILLB1</t>
+          <t>POAT220</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Gordon Power Station</t>
+          <t>Poatina Power Station</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -2156,52 +2156,52 @@
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0.9903</v>
+        <v>0.9725</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>1.0155</v>
+        <v>0.9929</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1.0012</v>
+        <v>0.9813</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>1.0024</v>
+        <v>0.9912</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>0.9984</v>
+        <v>0.9846</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>0.9859</v>
+        <v>0.9715</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>0.971</v>
+        <v>0.9691</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.9879</v>
+        <v>0.9771</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>0.993</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>0.9892</v>
+        <v>0.9802</v>
       </c>
       <c r="O25" s="5" t="inlineStr"/>
       <c r="P25" s="5" t="n">
-        <v>0.9918</v>
+        <v>0.9845</v>
       </c>
       <c r="Q25" s="5" t="inlineStr"/>
       <c r="R25" s="5" t="n">
-        <v>0.9918</v>
+        <v>0.9972</v>
       </c>
       <c r="S25" s="5" t="inlineStr"/>
       <c r="T25" s="5" t="n">
-        <v>0</v>
+        <v>0.0127</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V25" s="5" t="inlineStr"/>
       <c r="W25" s="6" t="inlineStr"/>
@@ -2209,66 +2209,66 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>L_W_CNL1</t>
+          <t>BBTHREE1</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
+          <t>Bell Bay Three Power Station</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0.9927</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>1.0079</v>
+        <v>1.0001</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.9979</v>
+        <v>1.0001</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>1.0006</v>
+        <v>1.0003</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>0.9958</v>
+        <v>0.9997</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>0.9865</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>0.9802</v>
+        <v>0.9982</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>0.991</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0.9819</v>
+        <v>0.9968</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>0.992</v>
+        <v>0.9977</v>
       </c>
       <c r="O26" s="5" t="inlineStr"/>
       <c r="P26" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.9986</v>
       </c>
       <c r="Q26" s="5" t="inlineStr"/>
       <c r="R26" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.9977</v>
       </c>
       <c r="S26" s="5" t="inlineStr"/>
       <c r="T26" s="5" t="n">
-        <v>0</v>
+        <v>-0.0009</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="V26" s="5" t="inlineStr"/>
       <c r="W26" s="6" t="inlineStr"/>
@@ -2276,66 +2276,66 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>WYA252B1</t>
+          <t>BBTHREE2</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
+          <t>Bell Bay Three Power Station</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0.9927</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>1.0079</v>
+        <v>1.0001</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.9979</v>
+        <v>1.0001</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>1.0006</v>
+        <v>1.0003</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>0.9958</v>
+        <v>0.9997</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>0.9865</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>0.9802</v>
+        <v>0.9982</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>0.991</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>0.9819</v>
+        <v>0.9968</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>0.992</v>
+        <v>0.9977</v>
       </c>
       <c r="O27" s="5" t="inlineStr"/>
       <c r="P27" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.9986</v>
       </c>
       <c r="Q27" s="5" t="inlineStr"/>
       <c r="R27" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.9977</v>
       </c>
       <c r="S27" s="5" t="inlineStr"/>
       <c r="T27" s="5" t="n">
-        <v>0</v>
+        <v>-0.0009</v>
       </c>
       <c r="U27" s="6" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="V27" s="5" t="inlineStr"/>
       <c r="W27" s="6" t="inlineStr"/>
@@ -2343,66 +2343,66 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>WYB252B1</t>
+          <t>BBTHREE3</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
+          <t>Bell Bay Three Power Station</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.9927</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>1.0079</v>
+        <v>1.0001</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.9979</v>
+        <v>1.0001</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>1.0006</v>
+        <v>1.0003</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>0.9958</v>
+        <v>0.9997</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>0.9865</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>0.9802</v>
+        <v>0.9982</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0.991</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0.9819</v>
+        <v>0.9968</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>0.992</v>
+        <v>0.9977</v>
       </c>
       <c r="O28" s="5" t="inlineStr"/>
       <c r="P28" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.9986</v>
       </c>
       <c r="Q28" s="5" t="inlineStr"/>
       <c r="R28" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.9977</v>
       </c>
       <c r="S28" s="5" t="inlineStr"/>
       <c r="T28" s="5" t="n">
-        <v>0</v>
+        <v>-0.0009</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="V28" s="5" t="inlineStr"/>
       <c r="W28" s="6" t="inlineStr"/>
@@ -2410,66 +2410,66 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>TREVALLN</t>
+          <t>TVPP104</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Trevallyn Power Station</t>
+          <t>Bell Bay Three Power Station</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.9857</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.9927</v>
+        <v>1.0001</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.9898</v>
+        <v>1.0001</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>0.9909</v>
+        <v>1.0003</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>0.9889</v>
+        <v>0.9997</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>0.9805</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>0.9848</v>
+        <v>0.9982</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>0.9891</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>0.9825</v>
+        <v>0.9968</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>0.99</v>
+        <v>0.9977</v>
       </c>
       <c r="O29" s="5" t="inlineStr"/>
       <c r="P29" s="5" t="n">
-        <v>0.9852</v>
+        <v>0.9986</v>
       </c>
       <c r="Q29" s="5" t="inlineStr"/>
       <c r="R29" s="5" t="n">
-        <v>0.997</v>
+        <v>0.9977</v>
       </c>
       <c r="S29" s="5" t="inlineStr"/>
       <c r="T29" s="5" t="n">
-        <v>0.0118</v>
+        <v>-0.0009</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>1.2</v>
+        <v>-0.09</v>
       </c>
       <c r="V29" s="5" t="inlineStr"/>
       <c r="W29" s="6" t="inlineStr"/>
@@ -2477,66 +2477,62 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>POAT220</t>
+          <t>BLNKTAS</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Poatina Power Station</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
+          <t>Basslink HVDC Link</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr"/>
       <c r="D30" s="4" t="n">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.9725</v>
+        <v>1</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.9929</v>
+        <v>1</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.9813</v>
+        <v>1</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>0.9912</v>
+        <v>1</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>0.9846</v>
+        <v>1</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>0.9715</v>
+        <v>1</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>0.9691</v>
+        <v>1</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>0.9771</v>
+        <v>1</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>0.9733000000000001</v>
+        <v>1</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>0.9802</v>
+        <v>1</v>
       </c>
       <c r="O30" s="5" t="inlineStr"/>
       <c r="P30" s="5" t="n">
-        <v>0.9845</v>
+        <v>1</v>
       </c>
       <c r="Q30" s="5" t="inlineStr"/>
       <c r="R30" s="5" t="n">
-        <v>0.9972</v>
+        <v>1</v>
       </c>
       <c r="S30" s="5" t="inlineStr"/>
       <c r="T30" s="5" t="n">
-        <v>0.0127</v>
+        <v>0</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V30" s="5" t="inlineStr"/>
       <c r="W30" s="6" t="inlineStr"/>
@@ -2544,12 +2540,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>TVPP104</t>
+          <t>TVCC201</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Bell Bay Three Power Station</t>
+          <t>Tamar Valley Combined Cycle Power Station</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2558,52 +2554,52 @@
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>58</v>
+        <v>208.6</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9996</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>1.0003</v>
+        <v>0.9999</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>0.9975000000000001</v>
+        <v>1</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>0.9982</v>
+        <v>1</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>0.9975000000000001</v>
+        <v>1</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>0.9968</v>
+        <v>1</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>0.9977</v>
+        <v>1</v>
       </c>
       <c r="O31" s="5" t="inlineStr"/>
       <c r="P31" s="5" t="n">
-        <v>0.9986</v>
+        <v>1</v>
       </c>
       <c r="Q31" s="5" t="inlineStr"/>
       <c r="R31" s="5" t="n">
-        <v>0.9977</v>
+        <v>1</v>
       </c>
       <c r="S31" s="5" t="inlineStr"/>
       <c r="T31" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0</v>
       </c>
       <c r="U31" s="6" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="V31" s="5" t="inlineStr"/>
       <c r="W31" s="6" t="inlineStr"/>
@@ -2611,66 +2607,62 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE3</t>
+          <t>DG_TAS1</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Bell Bay Three Power Station</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
+          <t>TAS1 Dummy Generator</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr"/>
       <c r="D32" s="4" t="n">
-        <v>35</v>
+        <v>3000</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.9995000000000001</v>
+        <v>1</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>1.0003</v>
+        <v>1</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>0.9975000000000001</v>
+        <v>1</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>0.9982</v>
+        <v>1</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>0.9975000000000001</v>
+        <v>1</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>0.9968</v>
+        <v>1</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>0.9977</v>
+        <v>1</v>
       </c>
       <c r="O32" s="5" t="inlineStr"/>
       <c r="P32" s="5" t="n">
-        <v>0.9986</v>
+        <v>1</v>
       </c>
       <c r="Q32" s="5" t="inlineStr"/>
       <c r="R32" s="5" t="n">
-        <v>0.9977</v>
+        <v>1</v>
       </c>
       <c r="S32" s="5" t="inlineStr"/>
       <c r="T32" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="V32" s="5" t="inlineStr"/>
       <c r="W32" s="6" t="inlineStr"/>
@@ -2678,66 +2670,66 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE1</t>
+          <t>LI_WY_CA</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Bell Bay Three Power Station</t>
+          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>35</v>
+        <v>173.7</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9915</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>1.0001</v>
+        <v>1.0028</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>1.0001</v>
+        <v>0.9919</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>1.0003</v>
+        <v>0.9977</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>0.9997</v>
+        <v>0.9936</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.9817</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>0.9982</v>
+        <v>0.9789</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.9845</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>0.9968</v>
+        <v>0.9809</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>0.9977</v>
+        <v>0.9899</v>
       </c>
       <c r="O33" s="5" t="inlineStr"/>
       <c r="P33" s="5" t="n">
-        <v>0.9986</v>
+        <v>0.9855</v>
       </c>
       <c r="Q33" s="5" t="inlineStr"/>
       <c r="R33" s="5" t="n">
-        <v>0.9977</v>
+        <v>1.0052</v>
       </c>
       <c r="S33" s="5" t="inlineStr"/>
       <c r="T33" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0197</v>
       </c>
       <c r="U33" s="6" t="n">
-        <v>-0.09</v>
+        <v>2</v>
       </c>
       <c r="V33" s="5" t="inlineStr"/>
       <c r="W33" s="6" t="inlineStr"/>
@@ -2745,66 +2737,66 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE2</t>
+          <t>REPULSE</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Bell Bay Three Power Station</t>
+          <t>Repulse Power Station</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9933</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>1.0001</v>
+        <v>1.0055</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>1.0001</v>
+        <v>0.9908</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>1.0003</v>
+        <v>1.0019</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>0.9997</v>
+        <v>0.9961</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.9855</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>0.9982</v>
+        <v>0.9798</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.985</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>0.9968</v>
+        <v>0.9857</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>0.9977</v>
+        <v>0.9922</v>
       </c>
       <c r="O34" s="5" t="inlineStr"/>
       <c r="P34" s="5" t="n">
-        <v>0.9986</v>
+        <v>0.9857</v>
       </c>
       <c r="Q34" s="5" t="inlineStr"/>
       <c r="R34" s="5" t="n">
-        <v>0.9977</v>
+        <v>1.0055</v>
       </c>
       <c r="S34" s="5" t="inlineStr"/>
       <c r="T34" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0198</v>
       </c>
       <c r="U34" s="6" t="n">
-        <v>-0.09</v>
+        <v>2.01</v>
       </c>
       <c r="V34" s="5" t="inlineStr"/>
       <c r="W34" s="6" t="inlineStr"/>
@@ -2812,62 +2804,66 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>DG_TAS1</t>
+          <t>CLUNY</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>TAS1 Dummy Generator</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr"/>
+          <t>Cluny Power Station</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
       <c r="D35" s="4" t="n">
-        <v>3000</v>
+        <v>19</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>1</v>
+        <v>0.9933</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>1</v>
+        <v>1.0055</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>1</v>
+        <v>0.9908</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>1</v>
+        <v>1.0019</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>1</v>
+        <v>0.9961</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>1</v>
+        <v>0.9855</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>1</v>
+        <v>0.9798</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>1</v>
+        <v>0.985</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>1</v>
+        <v>0.9857</v>
       </c>
       <c r="N35" s="5" t="n">
-        <v>1</v>
+        <v>0.9922</v>
       </c>
       <c r="O35" s="5" t="inlineStr"/>
       <c r="P35" s="5" t="n">
-        <v>1</v>
+        <v>0.9857</v>
       </c>
       <c r="Q35" s="5" t="inlineStr"/>
       <c r="R35" s="5" t="n">
-        <v>1</v>
+        <v>1.0055</v>
       </c>
       <c r="S35" s="5" t="inlineStr"/>
       <c r="T35" s="5" t="n">
-        <v>0</v>
+        <v>0.0198</v>
       </c>
       <c r="U35" s="6" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V35" s="5" t="inlineStr"/>
       <c r="W35" s="6" t="inlineStr"/>
@@ -2875,66 +2871,66 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TVCC201</t>
+          <t>WYA252B1</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Tamar Valley Combined Cycle Power Station</t>
+          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>208.6</v>
+        <v>25</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0.9996</v>
+        <v>0.9927</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>1</v>
+        <v>1.0079</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>1</v>
+        <v>0.9979</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>0.9999</v>
+        <v>1.0006</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>1</v>
+        <v>0.9958</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>1</v>
+        <v>0.9865</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>1</v>
+        <v>0.9802</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>1</v>
+        <v>0.991</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>1</v>
+        <v>0.9819</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>1</v>
+        <v>0.992</v>
       </c>
       <c r="O36" s="5" t="inlineStr"/>
       <c r="P36" s="5" t="n">
-        <v>1</v>
+        <v>0.9919</v>
       </c>
       <c r="Q36" s="5" t="inlineStr"/>
       <c r="R36" s="5" t="n">
-        <v>1</v>
+        <v>1.0075</v>
       </c>
       <c r="S36" s="5" t="inlineStr"/>
       <c r="T36" s="5" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
       <c r="U36" s="6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V36" s="5" t="inlineStr"/>
       <c r="W36" s="6" t="inlineStr"/>
@@ -2942,66 +2938,66 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>BLNKTAS</t>
+          <t>WYB252B1</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Basslink HVDC Link</t>
+          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>478</v>
+        <v>25</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>0.9927</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>1</v>
+        <v>1.0079</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1</v>
+        <v>0.9979</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>1</v>
+        <v>1.0006</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>1</v>
+        <v>0.9958</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>1</v>
+        <v>0.9865</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>1</v>
+        <v>0.9802</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>1</v>
+        <v>0.991</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>1</v>
+        <v>0.9819</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>1</v>
+        <v>0.992</v>
       </c>
       <c r="O37" s="5" t="inlineStr"/>
       <c r="P37" s="5" t="n">
-        <v>1</v>
+        <v>0.9919</v>
       </c>
       <c r="Q37" s="5" t="inlineStr"/>
       <c r="R37" s="5" t="n">
-        <v>1</v>
+        <v>1.0075</v>
       </c>
       <c r="S37" s="5" t="inlineStr"/>
       <c r="T37" s="5" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
       <c r="U37" s="6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V37" s="5" t="inlineStr"/>
       <c r="W37" s="6" t="inlineStr"/>
@@ -3009,7 +3005,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>LI_WY_CA</t>
+          <t>L_W_CNL1</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -3023,52 +3019,52 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>173.7</v>
+        <v>25</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.9915</v>
+        <v>0.9927</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>1.0028</v>
+        <v>1.0079</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.9979</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>0.9977</v>
+        <v>1.0006</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>0.9936</v>
+        <v>0.9958</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>0.9817</v>
+        <v>0.9865</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>0.9789</v>
+        <v>0.9802</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0.9845</v>
+        <v>0.991</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0.9809</v>
+        <v>0.9819</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>0.9899</v>
+        <v>0.992</v>
       </c>
       <c r="O38" s="5" t="inlineStr"/>
       <c r="P38" s="5" t="n">
-        <v>0.9855</v>
+        <v>0.9919</v>
       </c>
       <c r="Q38" s="5" t="inlineStr"/>
       <c r="R38" s="5" t="n">
-        <v>1.0052</v>
+        <v>1.0075</v>
       </c>
       <c r="S38" s="5" t="inlineStr"/>
       <c r="T38" s="5" t="n">
-        <v>0.0197</v>
+        <v>0.0156</v>
       </c>
       <c r="U38" s="6" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="V38" s="5" t="inlineStr"/>
       <c r="W38" s="6" t="inlineStr"/>
@@ -3076,66 +3072,58 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>REPULSE</t>
+          <t>CTHLWF1</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Repulse Power Station</t>
+          <t>Cattle Hill Wind Farm</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0.9933</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>1.0055</v>
-      </c>
-      <c r="G39" s="5" t="n">
+        <v>148</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="5" t="inlineStr"/>
+      <c r="I39" s="5" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>0.9809</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>0.9888</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>0.9836</v>
+      </c>
+      <c r="N39" s="5" t="n">
         <v>0.9908</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>1.0019</v>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>0.9961</v>
-      </c>
-      <c r="J39" s="5" t="n">
-        <v>0.9855</v>
-      </c>
-      <c r="K39" s="5" t="n">
-        <v>0.9798</v>
-      </c>
-      <c r="L39" s="5" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="M39" s="5" t="n">
-        <v>0.9857</v>
-      </c>
-      <c r="N39" s="5" t="n">
-        <v>0.9922</v>
       </c>
       <c r="O39" s="5" t="inlineStr"/>
       <c r="P39" s="5" t="n">
-        <v>0.9857</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="Q39" s="5" t="inlineStr"/>
       <c r="R39" s="5" t="n">
-        <v>1.0055</v>
+        <v>1.0088</v>
       </c>
       <c r="S39" s="5" t="inlineStr"/>
       <c r="T39" s="5" t="n">
-        <v>0.0198</v>
+        <v>0.0164</v>
       </c>
       <c r="U39" s="6" t="n">
-        <v>2.01</v>
+        <v>1.65</v>
       </c>
       <c r="V39" s="5" t="inlineStr"/>
       <c r="W39" s="6" t="inlineStr"/>
@@ -3143,12 +3131,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>CLUNY</t>
+          <t>MEADOWBK</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Cluny Power Station</t>
+          <t>Meadowbank Power Station</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -3157,52 +3145,52 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.9933</v>
+        <v>0.9737</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>1.0055</v>
+        <v>0.9756</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.9908</v>
+        <v>0.977</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>1.0019</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>0.9961</v>
+        <v>0.9716</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>0.9855</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>0.9798</v>
+        <v>0.983</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>0.985</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>0.9857</v>
+        <v>0.9688</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>0.9922</v>
+        <v>0.9872</v>
       </c>
       <c r="O40" s="5" t="inlineStr"/>
       <c r="P40" s="5" t="n">
-        <v>0.9857</v>
+        <v>0.9811</v>
       </c>
       <c r="Q40" s="5" t="inlineStr"/>
       <c r="R40" s="5" t="n">
-        <v>1.0055</v>
+        <v>1.0091</v>
       </c>
       <c r="S40" s="5" t="inlineStr"/>
       <c r="T40" s="5" t="n">
-        <v>0.0198</v>
+        <v>0.028</v>
       </c>
       <c r="U40" s="6" t="n">
-        <v>2.01</v>
+        <v>2.85</v>
       </c>
       <c r="V40" s="5" t="inlineStr"/>
       <c r="W40" s="6" t="inlineStr"/>
@@ -3210,58 +3198,66 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>CTHLWF1</t>
+          <t>PO110NL1</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Cattle Hill Wind Farm</t>
+          <t>Poatina Power Station</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>148</v>
-      </c>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="5" t="inlineStr"/>
-      <c r="G41" s="5" t="inlineStr"/>
-      <c r="H41" s="5" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.9911</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>1.0012</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.9937</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0.9943</v>
+      </c>
       <c r="I41" s="5" t="n">
-        <v>0.986</v>
+        <v>0.9902</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>0.985</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>0.9809</v>
+        <v>0.9815</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>0.9888</v>
+        <v>0.9774</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>0.9836</v>
+        <v>0.9726</v>
       </c>
       <c r="N41" s="5" t="n">
-        <v>0.9908</v>
+        <v>0.9846</v>
       </c>
       <c r="O41" s="5" t="inlineStr"/>
       <c r="P41" s="5" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9891</v>
       </c>
       <c r="Q41" s="5" t="inlineStr"/>
       <c r="R41" s="5" t="n">
-        <v>1.0088</v>
+        <v>1.012</v>
       </c>
       <c r="S41" s="5" t="inlineStr"/>
       <c r="T41" s="5" t="n">
-        <v>0.0164</v>
+        <v>0.0229</v>
       </c>
       <c r="U41" s="6" t="n">
-        <v>1.65</v>
+        <v>2.32</v>
       </c>
       <c r="V41" s="5" t="inlineStr"/>
       <c r="W41" s="6" t="inlineStr"/>
@@ -3269,12 +3265,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MEADOWBK</t>
+          <t>GOVILLB1</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Meadowbank Power Station</t>
+          <t>Gordon Power Station</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -3283,52 +3279,52 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.9737</v>
+        <v>0.9903</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.9756</v>
+        <v>1.0155</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.977</v>
+        <v>1.0012</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>0.9772999999999999</v>
+        <v>1.0024</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>0.9716</v>
+        <v>0.9984</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9859</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>0.983</v>
+        <v>0.971</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9879</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>0.9688</v>
+        <v>0.993</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>0.9872</v>
+        <v>0.9892</v>
       </c>
       <c r="O42" s="5" t="inlineStr"/>
       <c r="P42" s="5" t="n">
-        <v>0.9811</v>
+        <v>0.9918</v>
       </c>
       <c r="Q42" s="5" t="inlineStr"/>
       <c r="R42" s="5" t="n">
-        <v>1.0091</v>
+        <v>1.0141</v>
       </c>
       <c r="S42" s="5" t="inlineStr"/>
       <c r="T42" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0223</v>
       </c>
       <c r="U42" s="6" t="n">
-        <v>2.85</v>
+        <v>2.25</v>
       </c>
       <c r="V42" s="5" t="inlineStr"/>
       <c r="W42" s="6" t="inlineStr"/>
@@ -3384,14 +3380,14 @@
       </c>
       <c r="Q43" s="5" t="inlineStr"/>
       <c r="R43" s="5" t="n">
-        <v>1.0121</v>
+        <v>1.0368</v>
       </c>
       <c r="S43" s="5" t="inlineStr"/>
       <c r="T43" s="5" t="n">
-        <v>0</v>
+        <v>0.0247</v>
       </c>
       <c r="U43" s="6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V43" s="5" t="inlineStr"/>
       <c r="W43" s="6" t="inlineStr"/>
@@ -3399,12 +3395,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>CATAGUN1</t>
+          <t>PORTLAT1</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
+          <t>Port Latta Diesel Generator</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -3413,10 +3409,10 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.9915</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="F44" s="5" t="inlineStr"/>
       <c r="G44" s="5" t="inlineStr"/>
@@ -3440,12 +3436,12 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>MEADOWB2</t>
+          <t>GEORGTN2</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Meadowbank Power Station</t>
+          <t>GEORGE TOWN DIESEL</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
@@ -3453,7 +3449,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr"/>
       <c r="E45" s="5" t="n">
-        <v>0.9737</v>
+        <v>1.0092</v>
       </c>
       <c r="F45" s="5" t="inlineStr"/>
       <c r="G45" s="5" t="inlineStr"/>
@@ -3477,24 +3473,20 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>PORTLAT1</t>
+          <t>GEORGTN1</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Port Latta Diesel Generator</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>11</v>
-      </c>
+          <t>GEORGE TOWN DIESEL</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D46" s="3" t="inlineStr"/>
       <c r="E46" s="5" t="n">
-        <v>0.9602000000000001</v>
+        <v>1.0092</v>
       </c>
       <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="5" t="inlineStr"/>
@@ -3518,20 +3510,24 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>GEORGTN1</t>
+          <t>CATAGUN1</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>GEORGE TOWN DIESEL</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D47" s="3" t="inlineStr"/>
+          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>24</v>
+      </c>
       <c r="E47" s="5" t="n">
-        <v>1.0092</v>
+        <v>0.9915</v>
       </c>
       <c r="F47" s="5" t="inlineStr"/>
       <c r="G47" s="5" t="inlineStr"/>
@@ -3555,12 +3551,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>GEORGTN2</t>
+          <t>MEADOWB2</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>GEORGE TOWN DIESEL</t>
+          <t>Meadowbank Power Station</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -3568,7 +3564,7 @@
       </c>
       <c r="D48" s="3" t="inlineStr"/>
       <c r="E48" s="5" t="n">
-        <v>1.0092</v>
+        <v>0.9737</v>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="5" t="inlineStr"/>
@@ -3592,12 +3588,12 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>BBDISEL1</t>
+          <t>QUERIVE1</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Bell Bay Power Station</t>
+          <t>Que River Diesel</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -3606,13 +3602,13 @@
         </is>
       </c>
       <c r="D49" s="4" t="n">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0.9998</v>
+        <v>0.9099</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>1.0003</v>
+        <v>0.9759</v>
       </c>
       <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr"/>
@@ -3635,12 +3631,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>QUERIVE1</t>
+          <t>BBDISEL1</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Que River Diesel</t>
+          <t>Bell Bay Power Station</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -3649,13 +3645,13 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.9458</v>
+        <v>0.9998</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.9759</v>
+        <v>1.0003</v>
       </c>
       <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr"/>
@@ -4303,268 +4299,268 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>TRIBNL1</t>
+          <t>JBUTTERS</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0.9641999999999999</v>
+        <v>0.9384</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.971</v>
+        <v>0.9456</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.9607</v>
+        <v>0.9445</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.9552</v>
+        <v>0.9365</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.9611</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.9454</v>
+        <v>0.923</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.9369</v>
+        <v>0.9258</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.9582000000000001</v>
+        <v>0.9395</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.9373</v>
+        <v>0.9208</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.9542</v>
+        <v>0.9245</v>
       </c>
       <c r="L12" s="5" t="inlineStr"/>
       <c r="M12" s="5" t="n">
-        <v>0.9586</v>
+        <v>0.9386</v>
       </c>
       <c r="N12" s="5" t="inlineStr"/>
       <c r="O12" s="5" t="n">
-        <v>0.9586</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="P12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>JBUTTERS</t>
+          <t>BASTYAN</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0.9384</v>
+        <v>0.9466</v>
       </c>
       <c r="C13" s="5" t="n">
+        <v>0.9496</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.9486</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="F13" s="5" t="n">
         <v>0.9456</v>
       </c>
-      <c r="D13" s="5" t="n">
-        <v>0.9445</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>0.9365</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>0.9370000000000001</v>
-      </c>
       <c r="G13" s="5" t="n">
-        <v>0.923</v>
+        <v>0.9301</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.9258</v>
+        <v>0.9286</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.9395</v>
+        <v>0.9334</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.9208</v>
+        <v>0.9202</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.9245</v>
+        <v>0.9313</v>
       </c>
       <c r="L13" s="5" t="inlineStr"/>
       <c r="M13" s="5" t="n">
-        <v>0.9386</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="N13" s="5" t="inlineStr"/>
       <c r="O13" s="5" t="n">
-        <v>0.9602000000000001</v>
+        <v>0.9623</v>
       </c>
       <c r="P13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>BASTYAN</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>0.9466</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>0.9496</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>0.9486</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>0.9409999999999999</v>
-      </c>
+          <t>GRANWF1</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
       <c r="F14" s="5" t="n">
-        <v>0.9456</v>
+        <v>0.959</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.9301</v>
+        <v>0.9408</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.9286</v>
+        <v>0.9314</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.9334</v>
+        <v>0.9543</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.9202</v>
+        <v>0.9388</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.9313</v>
+        <v>0.9473</v>
       </c>
       <c r="L14" s="5" t="inlineStr"/>
       <c r="M14" s="5" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9555</v>
       </c>
       <c r="N14" s="5" t="inlineStr"/>
       <c r="O14" s="5" t="n">
-        <v>0.9623</v>
+        <v>0.9688</v>
       </c>
       <c r="P14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>GRANWF1</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="inlineStr"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="inlineStr"/>
+          <t>CETHANA</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0.9671</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9723000000000001</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9628</v>
+      </c>
       <c r="F15" s="5" t="n">
-        <v>0.959</v>
+        <v>0.9658</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.9408</v>
+        <v>0.9545</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.9314</v>
+        <v>0.9512</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.9543</v>
+        <v>0.9544</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.9388</v>
+        <v>0.9504</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.9473</v>
+        <v>0.958</v>
       </c>
       <c r="L15" s="5" t="inlineStr"/>
       <c r="M15" s="5" t="n">
-        <v>0.9555</v>
+        <v>0.9473</v>
       </c>
       <c r="N15" s="5" t="inlineStr"/>
       <c r="O15" s="5" t="n">
-        <v>0.9688</v>
+        <v>0.9705</v>
       </c>
       <c r="P15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>CETHANA</t>
+          <t>DEVILS_G</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>0.9671</v>
+        <v>0.9719</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.963</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="E16" s="5" t="n">
+        <v>0.9692</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.9698</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.9618</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0.9566</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>0.9594</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>0.9537</v>
+      </c>
+      <c r="K16" s="5" t="n">
         <v>0.9628</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>0.9658</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>0.9545</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>0.9512</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>0.9544</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>0.9504</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>0.958</v>
       </c>
       <c r="L16" s="5" t="inlineStr"/>
       <c r="M16" s="5" t="n">
-        <v>0.9473</v>
+        <v>0.9616</v>
       </c>
       <c r="N16" s="5" t="inlineStr"/>
       <c r="O16" s="5" t="n">
-        <v>0.9705</v>
+        <v>0.9761</v>
       </c>
       <c r="P16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>DEVILS_G</t>
+          <t>TRIBNL1</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>0.9719</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.97</v>
+        <v>0.971</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.9607</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.9692</v>
+        <v>0.9552</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.9698</v>
+        <v>0.9611</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.9618</v>
+        <v>0.9454</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.9566</v>
+        <v>0.9369</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.9594</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.9537</v>
+        <v>0.9373</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.9628</v>
+        <v>0.9542</v>
       </c>
       <c r="L17" s="5" t="inlineStr"/>
       <c r="M17" s="5" t="n">
-        <v>0.9616</v>
+        <v>0.9586</v>
       </c>
       <c r="N17" s="5" t="inlineStr"/>
       <c r="O17" s="5" t="n">
-        <v>0.9761</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="P17" s="5" t="inlineStr"/>
     </row>
@@ -4755,42 +4751,42 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>POAT110</t>
+          <t>GORDON</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>0.963</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9676</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.9677</v>
+        <v>0.9594</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.9799</v>
+        <v>0.9868</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.9728</v>
+        <v>0.9594</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>0.9512</v>
+        <v>0.928</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.9625</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0.9555</v>
+        <v>0.9731</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.9641</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.9594</v>
       </c>
       <c r="N22" s="5" t="inlineStr"/>
       <c r="O22" s="5" t="n">
@@ -4801,42 +4797,42 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GORDON</t>
+          <t>POAT110</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.963</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.9676</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0.9594</v>
+        <v>0.9677</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.9868</v>
+        <v>0.9799</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.9594</v>
+        <v>0.9728</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>0.928</v>
+        <v>0.9512</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9625</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0.9731</v>
+        <v>0.9555</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9641</v>
       </c>
       <c r="L23" s="5" t="inlineStr"/>
       <c r="M23" s="5" t="n">
-        <v>0.9594</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="N23" s="5" t="inlineStr"/>
       <c r="O23" s="5" t="n">
@@ -4847,866 +4843,866 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>PO110NL1</t>
+          <t>TREVALLN</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>0.9911</v>
+        <v>0.9857</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>1.0012</v>
+        <v>0.9927</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0.9937</v>
+        <v>0.9898</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.9943</v>
+        <v>0.9909</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.9902</v>
+        <v>0.9889</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.9805</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0.9815</v>
+        <v>0.9848</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0.9774</v>
+        <v>0.9891</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0.9726</v>
+        <v>0.9825</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0.9846</v>
+        <v>0.99</v>
       </c>
       <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="n">
-        <v>0.9891</v>
+        <v>0.9852</v>
       </c>
       <c r="N24" s="5" t="inlineStr"/>
       <c r="O24" s="5" t="n">
-        <v>0.9891</v>
+        <v>0.997</v>
       </c>
       <c r="P24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>GOVILLB1</t>
+          <t>POAT220</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>0.9903</v>
+        <v>0.9725</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1.0155</v>
+        <v>0.9929</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1.0012</v>
+        <v>0.9813</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1.0024</v>
+        <v>0.9912</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.9984</v>
+        <v>0.9846</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.9859</v>
+        <v>0.9715</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>0.971</v>
+        <v>0.9691</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>0.9879</v>
+        <v>0.9771</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>0.993</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>0.9892</v>
+        <v>0.9802</v>
       </c>
       <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="n">
-        <v>0.9918</v>
+        <v>0.9845</v>
       </c>
       <c r="N25" s="5" t="inlineStr"/>
       <c r="O25" s="5" t="n">
-        <v>0.9918</v>
+        <v>0.9972</v>
       </c>
       <c r="P25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>L_W_CNL1</t>
+          <t>BBTHREE1</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>0.9927</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>1.0079</v>
+        <v>1.0001</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>0.9979</v>
+        <v>1.0001</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1.0006</v>
+        <v>1.0003</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.9958</v>
+        <v>0.9997</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.9865</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>0.9802</v>
+        <v>0.9982</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>0.991</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>0.9819</v>
+        <v>0.9968</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>0.992</v>
+        <v>0.9977</v>
       </c>
       <c r="L26" s="5" t="inlineStr"/>
       <c r="M26" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.9986</v>
       </c>
       <c r="N26" s="5" t="inlineStr"/>
       <c r="O26" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.9977</v>
       </c>
       <c r="P26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>WYA252B1</t>
+          <t>BBTHREE2</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>0.9927</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1.0079</v>
+        <v>1.0001</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0.9979</v>
+        <v>1.0001</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1.0006</v>
+        <v>1.0003</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.9958</v>
+        <v>0.9997</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.9865</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>0.9802</v>
+        <v>0.9982</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>0.991</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>0.9819</v>
+        <v>0.9968</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>0.992</v>
+        <v>0.9977</v>
       </c>
       <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.9986</v>
       </c>
       <c r="N27" s="5" t="inlineStr"/>
       <c r="O27" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.9977</v>
       </c>
       <c r="P27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>WYB252B1</t>
+          <t>BBTHREE3</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>0.9927</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>1.0079</v>
+        <v>1.0001</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>0.9979</v>
+        <v>1.0001</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1.0006</v>
+        <v>1.0003</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.9958</v>
+        <v>0.9997</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.9865</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0.9802</v>
+        <v>0.9982</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>0.991</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>0.9819</v>
+        <v>0.9968</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>0.992</v>
+        <v>0.9977</v>
       </c>
       <c r="L28" s="5" t="inlineStr"/>
       <c r="M28" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.9986</v>
       </c>
       <c r="N28" s="5" t="inlineStr"/>
       <c r="O28" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.9977</v>
       </c>
       <c r="P28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>TREVALLN</t>
+          <t>TVPP104</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>0.9857</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>0.9927</v>
+        <v>1.0001</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>0.9898</v>
+        <v>1.0001</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.9909</v>
+        <v>1.0003</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.9889</v>
+        <v>0.9997</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.9805</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>0.9848</v>
+        <v>0.9982</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>0.9891</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>0.9825</v>
+        <v>0.9968</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>0.99</v>
+        <v>0.9977</v>
       </c>
       <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="n">
-        <v>0.9852</v>
+        <v>0.9986</v>
       </c>
       <c r="N29" s="5" t="inlineStr"/>
       <c r="O29" s="5" t="n">
-        <v>0.997</v>
+        <v>0.9977</v>
       </c>
       <c r="P29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>POAT220</t>
+          <t>BLNKTAS</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>0.9725</v>
+        <v>1</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>0.9929</v>
+        <v>1</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>0.9813</v>
+        <v>1</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.9912</v>
+        <v>1</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.9846</v>
+        <v>1</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.9715</v>
+        <v>1</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>0.9691</v>
+        <v>1</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>0.9771</v>
+        <v>1</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>0.9733000000000001</v>
+        <v>1</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>0.9802</v>
+        <v>1</v>
       </c>
       <c r="L30" s="5" t="inlineStr"/>
       <c r="M30" s="5" t="n">
-        <v>0.9845</v>
+        <v>1</v>
       </c>
       <c r="N30" s="5" t="inlineStr"/>
       <c r="O30" s="5" t="n">
-        <v>0.9972</v>
+        <v>1</v>
       </c>
       <c r="P30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>TVPP104</t>
+          <t>TVCC201</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9996</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1.0003</v>
+        <v>0.9999</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.9975000000000001</v>
+        <v>1</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>0.9982</v>
+        <v>1</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>0.9975000000000001</v>
+        <v>1</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>0.9968</v>
+        <v>1</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>0.9977</v>
+        <v>1</v>
       </c>
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="n">
-        <v>0.9986</v>
+        <v>1</v>
       </c>
       <c r="N31" s="5" t="inlineStr"/>
       <c r="O31" s="5" t="n">
-        <v>0.9977</v>
+        <v>1</v>
       </c>
       <c r="P31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE3</t>
+          <t>DG_TAS1</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>0.9995000000000001</v>
+        <v>1</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>1.0003</v>
+        <v>1</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.9975000000000001</v>
+        <v>1</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>0.9982</v>
+        <v>1</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>0.9975000000000001</v>
+        <v>1</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>0.9968</v>
+        <v>1</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>0.9977</v>
+        <v>1</v>
       </c>
       <c r="L32" s="5" t="inlineStr"/>
       <c r="M32" s="5" t="n">
-        <v>0.9986</v>
+        <v>1</v>
       </c>
       <c r="N32" s="5" t="inlineStr"/>
       <c r="O32" s="5" t="n">
-        <v>0.9977</v>
+        <v>1</v>
       </c>
       <c r="P32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE1</t>
+          <t>LI_WY_CA</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9915</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>1.0001</v>
+        <v>1.0028</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>1.0001</v>
+        <v>0.9919</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>1.0003</v>
+        <v>0.9977</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.9997</v>
+        <v>0.9936</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.9817</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>0.9982</v>
+        <v>0.9789</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.9845</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>0.9968</v>
+        <v>0.9809</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>0.9977</v>
+        <v>0.9899</v>
       </c>
       <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="n">
-        <v>0.9986</v>
+        <v>0.9855</v>
       </c>
       <c r="N33" s="5" t="inlineStr"/>
       <c r="O33" s="5" t="n">
-        <v>0.9977</v>
+        <v>1.0052</v>
       </c>
       <c r="P33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE2</t>
+          <t>REPULSE</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9933</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>1.0001</v>
+        <v>1.0055</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>1.0001</v>
+        <v>0.9908</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>1.0003</v>
+        <v>1.0019</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.9997</v>
+        <v>0.9961</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.9855</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>0.9982</v>
+        <v>0.9798</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.985</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>0.9968</v>
+        <v>0.9857</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>0.9977</v>
+        <v>0.9922</v>
       </c>
       <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="5" t="n">
-        <v>0.9986</v>
+        <v>0.9857</v>
       </c>
       <c r="N34" s="5" t="inlineStr"/>
       <c r="O34" s="5" t="n">
-        <v>0.9977</v>
+        <v>1.0055</v>
       </c>
       <c r="P34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>DG_TAS1</t>
+          <t>CLUNY</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1</v>
+        <v>0.9933</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>1</v>
+        <v>1.0055</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>1</v>
+        <v>0.9908</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>1</v>
+        <v>1.0019</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>1</v>
+        <v>0.9961</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>1</v>
+        <v>0.9855</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>1</v>
+        <v>0.9798</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>1</v>
+        <v>0.985</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>1</v>
+        <v>0.9857</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>1</v>
+        <v>0.9922</v>
       </c>
       <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="n">
-        <v>1</v>
+        <v>0.9857</v>
       </c>
       <c r="N35" s="5" t="inlineStr"/>
       <c r="O35" s="5" t="n">
-        <v>1</v>
+        <v>1.0055</v>
       </c>
       <c r="P35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TVCC201</t>
+          <t>WYA252B1</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>0.9996</v>
+        <v>0.9927</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>1</v>
+        <v>1.0079</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>1</v>
+        <v>0.9979</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0.9999</v>
+        <v>1.0006</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>1</v>
+        <v>0.9958</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>1</v>
+        <v>0.9865</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>1</v>
+        <v>0.9802</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>1</v>
+        <v>0.991</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>1</v>
+        <v>0.9819</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>1</v>
+        <v>0.992</v>
       </c>
       <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="5" t="n">
-        <v>1</v>
+        <v>0.9919</v>
       </c>
       <c r="N36" s="5" t="inlineStr"/>
       <c r="O36" s="5" t="n">
-        <v>1</v>
+        <v>1.0075</v>
       </c>
       <c r="P36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>BLNKTAS</t>
+          <t>WYB252B1</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1</v>
+        <v>0.9927</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>1</v>
+        <v>1.0079</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>1</v>
+        <v>0.9979</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>1.0006</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>1</v>
+        <v>0.9958</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1</v>
+        <v>0.9865</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>1</v>
+        <v>0.9802</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>1</v>
+        <v>0.991</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>1</v>
+        <v>0.9819</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>1</v>
+        <v>0.992</v>
       </c>
       <c r="L37" s="5" t="inlineStr"/>
       <c r="M37" s="5" t="n">
-        <v>1</v>
+        <v>0.9919</v>
       </c>
       <c r="N37" s="5" t="inlineStr"/>
       <c r="O37" s="5" t="n">
-        <v>1</v>
+        <v>1.0075</v>
       </c>
       <c r="P37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>LI_WY_CA</t>
+          <t>L_W_CNL1</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>0.9915</v>
+        <v>0.9927</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>1.0028</v>
+        <v>1.0079</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.9979</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.9977</v>
+        <v>1.0006</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.9936</v>
+        <v>0.9958</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.9817</v>
+        <v>0.9865</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>0.9789</v>
+        <v>0.9802</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>0.9845</v>
+        <v>0.991</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>0.9809</v>
+        <v>0.9819</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>0.9899</v>
+        <v>0.992</v>
       </c>
       <c r="L38" s="5" t="inlineStr"/>
       <c r="M38" s="5" t="n">
-        <v>0.9855</v>
+        <v>0.9919</v>
       </c>
       <c r="N38" s="5" t="inlineStr"/>
       <c r="O38" s="5" t="n">
-        <v>1.0052</v>
+        <v>1.0075</v>
       </c>
       <c r="P38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>REPULSE</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="n">
-        <v>0.9933</v>
-      </c>
-      <c r="C39" s="5" t="n">
-        <v>1.0055</v>
-      </c>
-      <c r="D39" s="5" t="n">
+          <t>CTHLWF1</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr"/>
+      <c r="C39" s="5" t="inlineStr"/>
+      <c r="D39" s="5" t="inlineStr"/>
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>0.9809</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>0.9888</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>0.9836</v>
+      </c>
+      <c r="K39" s="5" t="n">
         <v>0.9908</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>1.0019</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>0.9961</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0.9855</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>0.9798</v>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="J39" s="5" t="n">
-        <v>0.9857</v>
-      </c>
-      <c r="K39" s="5" t="n">
-        <v>0.9922</v>
       </c>
       <c r="L39" s="5" t="inlineStr"/>
       <c r="M39" s="5" t="n">
-        <v>0.9857</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="N39" s="5" t="inlineStr"/>
       <c r="O39" s="5" t="n">
-        <v>1.0055</v>
+        <v>1.0088</v>
       </c>
       <c r="P39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>CLUNY</t>
+          <t>MEADOWBK</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>0.9933</v>
+        <v>0.9737</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>1.0055</v>
+        <v>0.9756</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>0.9908</v>
+        <v>0.977</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>1.0019</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.9961</v>
+        <v>0.9716</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.9855</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>0.9798</v>
+        <v>0.983</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>0.985</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>0.9857</v>
+        <v>0.9688</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>0.9922</v>
+        <v>0.9872</v>
       </c>
       <c r="L40" s="5" t="inlineStr"/>
       <c r="M40" s="5" t="n">
-        <v>0.9857</v>
+        <v>0.9811</v>
       </c>
       <c r="N40" s="5" t="inlineStr"/>
       <c r="O40" s="5" t="n">
-        <v>1.0055</v>
+        <v>1.0091</v>
       </c>
       <c r="P40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>CTHLWF1</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr"/>
-      <c r="C41" s="5" t="inlineStr"/>
-      <c r="D41" s="5" t="inlineStr"/>
-      <c r="E41" s="5" t="inlineStr"/>
+          <t>PO110NL1</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0.9911</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>1.0012</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0.9937</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.9943</v>
+      </c>
       <c r="F41" s="5" t="n">
-        <v>0.986</v>
+        <v>0.9902</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.985</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>0.9809</v>
+        <v>0.9815</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>0.9888</v>
+        <v>0.9774</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>0.9836</v>
+        <v>0.9726</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>0.9908</v>
+        <v>0.9846</v>
       </c>
       <c r="L41" s="5" t="inlineStr"/>
       <c r="M41" s="5" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9891</v>
       </c>
       <c r="N41" s="5" t="inlineStr"/>
       <c r="O41" s="5" t="n">
-        <v>1.0088</v>
+        <v>1.012</v>
       </c>
       <c r="P41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MEADOWBK</t>
+          <t>GOVILLB1</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>0.9737</v>
+        <v>0.9903</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>0.9756</v>
+        <v>1.0155</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>0.977</v>
+        <v>1.0012</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.9772999999999999</v>
+        <v>1.0024</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.9716</v>
+        <v>0.9984</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9859</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>0.983</v>
+        <v>0.971</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9879</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>0.9688</v>
+        <v>0.993</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>0.9872</v>
+        <v>0.9892</v>
       </c>
       <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="n">
-        <v>0.9811</v>
+        <v>0.9918</v>
       </c>
       <c r="N42" s="5" t="inlineStr"/>
       <c r="O42" s="5" t="n">
-        <v>1.0091</v>
+        <v>1.0141</v>
       </c>
       <c r="P42" s="5" t="inlineStr"/>
     </row>
@@ -5752,18 +5748,18 @@
       </c>
       <c r="N43" s="5" t="inlineStr"/>
       <c r="O43" s="5" t="n">
-        <v>1.0121</v>
+        <v>1.0368</v>
       </c>
       <c r="P43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>CATAGUN1</t>
+          <t>PORTLAT1</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>0.9915</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="C44" s="5" t="inlineStr"/>
       <c r="D44" s="5" t="inlineStr"/>
@@ -5783,11 +5779,11 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>MEADOWB2</t>
+          <t>GEORGTN2</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>0.9737</v>
+        <v>1.0092</v>
       </c>
       <c r="C45" s="5" t="inlineStr"/>
       <c r="D45" s="5" t="inlineStr"/>
@@ -5807,11 +5803,11 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>PORTLAT1</t>
+          <t>GEORGTN1</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>0.9602000000000001</v>
+        <v>1.0092</v>
       </c>
       <c r="C46" s="5" t="inlineStr"/>
       <c r="D46" s="5" t="inlineStr"/>
@@ -5831,11 +5827,11 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>GEORGTN1</t>
+          <t>CATAGUN1</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1.0092</v>
+        <v>0.9915</v>
       </c>
       <c r="C47" s="5" t="inlineStr"/>
       <c r="D47" s="5" t="inlineStr"/>
@@ -5855,11 +5851,11 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>GEORGTN2</t>
+          <t>MEADOWB2</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>1.0092</v>
+        <v>0.9737</v>
       </c>
       <c r="C48" s="5" t="inlineStr"/>
       <c r="D48" s="5" t="inlineStr"/>
@@ -5879,14 +5875,14 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>BBDISEL1</t>
+          <t>QUERIVE1</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>0.9998</v>
+        <v>0.9099</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>1.0003</v>
+        <v>0.9759</v>
       </c>
       <c r="D49" s="5" t="inlineStr"/>
       <c r="E49" s="5" t="inlineStr"/>
@@ -5905,14 +5901,14 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>QUERIVE1</t>
+          <t>BBDISEL1</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>0.9458</v>
+        <v>0.9998</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>0.9759</v>
+        <v>1.0003</v>
       </c>
       <c r="D50" s="5" t="inlineStr"/>
       <c r="E50" s="5" t="inlineStr"/>
@@ -6212,7 +6208,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>TVPP104</t>
+          <t>BBTHREE1</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -6241,7 +6237,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE3</t>
+          <t>BBTHREE2</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -6270,7 +6266,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE1</t>
+          <t>BBTHREE3</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -6299,7 +6295,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE2</t>
+          <t>TVPP104</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -6328,24 +6324,20 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>TRIBNL1</t>
+          <t>BLNKTAS</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Tribute Power Station</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
+          <t>Basslink HVDC Link</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="5" t="n">
-        <v>0.9586</v>
+        <v>1</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.9586</v>
+        <v>1</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0</v>
@@ -6357,24 +6349,24 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>PO110NL1</t>
+          <t>TVCC201</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Poatina Power Station</t>
+          <t>Tamar Valley Combined Cycle Power Station</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.9891</v>
+        <v>1</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.9891</v>
+        <v>1</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>0</v>
@@ -6386,24 +6378,20 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>GOVILLB1</t>
+          <t>DG_TAS1</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Gordon Power Station</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
+          <t>TAS1 Dummy Generator</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="5" t="n">
-        <v>0.9918</v>
+        <v>1</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.9918</v>
+        <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>0</v>
@@ -6415,12 +6403,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>L_W_CNL1</t>
+          <t>BUTLERSG</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
+          <t>Butlers Gorge Power Station</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -6429,56 +6417,56 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.9475</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.9396</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>WYA252B1</t>
+          <t>MUSSELR1</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
+          <t>Musselroe Wind Farm</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.9188</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.9101</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>WYB252B1</t>
+          <t>POAT110</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
+          <t>Poatina Power Station</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -6487,135 +6475,143 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.9872</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0</v>
+        <v>0.0109</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>DG_TAS1</t>
+          <t>TREVALLN</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>TAS1 Dummy Generator</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr"/>
+          <t>Trevallyn Power Station</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
       <c r="D13" s="5" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1</v>
+        <v>0.9852</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0</v>
+        <v>0.0118</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>TVCC201</t>
+          <t>POAT220</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Tamar Valley Combined Cycle Power Station</t>
+          <t>Poatina Power Station</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1</v>
+        <v>0.9972</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1</v>
+        <v>0.9845</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0</v>
+        <v>0.0127</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>BLNKTAS</t>
+          <t>GRANWF1</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Basslink HVDC Link</t>
+          <t>Granville Harbour Wind Farm</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>0.9688</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1</v>
+        <v>0.9555</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0</v>
+        <v>0.0133</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>MIDLDPS1</t>
+          <t>DEVILS_G</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Midlands Power Station</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr"/>
+          <t>Devils Gate Power Station</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
       <c r="D16" s="5" t="n">
-        <v>1.0121</v>
+        <v>0.9761</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1.0121</v>
+        <v>0.9616</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0</v>
+        <v>0.0145</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>BUTLERSG</t>
+          <t>LK_ECHO</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Butlers Gorge Power Station</t>
+          <t>Lake Echo Power Station</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -6624,27 +6620,27 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.9475</v>
+        <v>0.946</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.9396</v>
+        <v>0.9314</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0146</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.84</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>MUSSELR1</t>
+          <t>WOOLNTH1</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Musselroe Wind Farm</t>
+          <t>Woolnorth Studland Bay / Bluff Point Wind Farm</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -6653,27 +6649,27 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.9188</v>
+        <v>0.9371</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.9101</v>
+        <v>0.9224</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0147</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.96</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>POAT110</t>
+          <t>PALOONA</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Poatina Power Station</t>
+          <t>Paloona Power Station</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -6682,27 +6678,27 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0.9872</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.9648</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.0109</v>
+        <v>0.0155</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>1.12</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>TREVALLN</t>
+          <t>WYA252B1</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Trevallyn Power Station</t>
+          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -6711,27 +6707,27 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0.997</v>
+        <v>1.0075</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.9852</v>
+        <v>0.9919</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.0118</v>
+        <v>0.0156</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>POAT220</t>
+          <t>WYB252B1</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Poatina Power Station</t>
+          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -6740,45 +6736,45 @@
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0.9972</v>
+        <v>1.0075</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.9845</v>
+        <v>0.9919</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.0127</v>
+        <v>0.0156</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>GRANWF1</t>
+          <t>L_W_CNL1</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Granville Harbour Wind Farm</t>
+          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.9688</v>
+        <v>1.0075</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.9555</v>
+        <v>0.9919</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0156</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="25">
@@ -7060,41 +7056,37 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>TRIBUTE</t>
+          <t>MIDLDPS1</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Tribute Power Station</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
+          <t>Midlands Power Station</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr"/>
       <c r="D35" s="5" t="n">
-        <v>0.9505</v>
+        <v>1.0368</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0.9265</v>
+        <v>1.0121</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.024</v>
+        <v>0.0247</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>2.59</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>CETHANA</t>
+          <t>TRIBUTE</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Cethana Power Station</t>
+          <t>Tribute Power Station</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -7103,27 +7095,27 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>0.9705</v>
+        <v>0.9505</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0.9473</v>
+        <v>0.9265</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.0232</v>
+        <v>0.024</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>MACKNTSH</t>
+          <t>CETHANA</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Mackintosh Power Station</t>
+          <t>Cethana Power Station</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -7132,27 +7124,27 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>0.9429</v>
+        <v>0.9705</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0.92</v>
+        <v>0.9473</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.0229</v>
+        <v>0.0232</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>JBUTTERS</t>
+          <t>MACKNTSH</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>John Butters Power Station</t>
+          <t>Mackintosh Power Station</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -7161,27 +7153,27 @@
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>0.9602000000000001</v>
+        <v>0.9429</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.9386</v>
+        <v>0.92</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.0216</v>
+        <v>0.0229</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>REPULSE</t>
+          <t>PO110NL1</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Repulse Power Station</t>
+          <t>Poatina Power Station</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -7190,27 +7182,27 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>1.0055</v>
+        <v>1.012</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0.9857</v>
+        <v>0.9891</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.0198</v>
+        <v>0.0229</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>2.01</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>CLUNY</t>
+          <t>GOVILLB1</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Cluny Power Station</t>
+          <t>Gordon Power Station</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -7219,27 +7211,27 @@
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>1.0055</v>
+        <v>1.0141</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.9857</v>
+        <v>0.9918</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.0198</v>
+        <v>0.0223</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>LI_WY_CA</t>
+          <t>JBUTTERS</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
+          <t>John Butters Power Station</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -7248,27 +7240,27 @@
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>1.0052</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0.9855</v>
+        <v>0.9386</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.0197</v>
+        <v>0.0216</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>LEM_WIL</t>
+          <t>TRIBNL1</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Lemonthyme / Wilmot Power Station</t>
+          <t>Tribute Power Station</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -7277,56 +7269,56 @@
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>0.9863</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.9676</v>
+        <v>0.9586</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.0187</v>
+        <v>0.0207</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>CTHLWF1</t>
+          <t>REPULSE</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Cattle Hill Wind Farm</t>
+          <t>Repulse Power Station</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>1.0088</v>
+        <v>1.0055</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9857</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.0164</v>
+        <v>0.0198</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>1.65</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TARRALEA</t>
+          <t>CLUNY</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Tarraleah Power Station</t>
+          <t>Cluny Power Station</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -7335,27 +7327,27 @@
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>0.9581</v>
+        <v>1.0055</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.9419</v>
+        <v>0.9857</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.0162</v>
+        <v>0.0198</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>PALOONA</t>
+          <t>LI_WY_CA</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Paloona Power Station</t>
+          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -7364,45 +7356,45 @@
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>0.9802999999999999</v>
+        <v>1.0052</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0.9648</v>
+        <v>0.9855</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.0155</v>
+        <v>0.0197</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>WOOLNTH1</t>
+          <t>LEM_WIL</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Woolnorth Studland Bay / Bluff Point Wind Farm</t>
+          <t>Lemonthyme / Wilmot Power Station</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>0.9371</v>
+        <v>0.9863</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0.9224</v>
+        <v>0.9676</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.0147</v>
+        <v>0.0187</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>1.59</v>
+        <v>1.93</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/TAS_mlf.xlsx
+++ b/outputs/TAS_mlf.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2209,7 +2209,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE1</t>
+          <t>TVPP104</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>0.9995000000000001</v>
@@ -2276,7 +2276,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE2</t>
+          <t>BBTHREE3</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2343,7 +2343,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE3</t>
+          <t>BBTHREE2</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2410,7 +2410,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>TVPP104</t>
+          <t>BBTHREE1</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>0.9995000000000001</v>
@@ -2485,9 +2485,13 @@
           <t>Basslink HVDC Link</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
       <c r="D30" s="4" t="n">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>1</v>
@@ -2540,24 +2544,20 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>TVCC201</t>
+          <t>DG_TAS1</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Tamar Valley Combined Cycle Power Station</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
+          <t>TAS1 Dummy Generator</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr"/>
       <c r="D31" s="4" t="n">
-        <v>208.6</v>
+        <v>3000</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="F31" s="5" t="n">
         <v>1</v>
@@ -2566,7 +2566,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="I31" s="5" t="n">
         <v>1</v>
@@ -2607,20 +2607,24 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>DG_TAS1</t>
+          <t>TVCC201</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>TAS1 Dummy Generator</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr"/>
+          <t>Tamar Valley Combined Cycle Power Station</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
       <c r="D32" s="4" t="n">
-        <v>3000</v>
+        <v>208.6</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>1</v>
@@ -2629,7 +2633,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>1</v>
@@ -2737,12 +2741,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>REPULSE</t>
+          <t>CLUNY</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Repulse Power Station</t>
+          <t>Cluny Power Station</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -2751,7 +2755,7 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E34" s="5" t="n">
         <v>0.9933</v>
@@ -2804,12 +2808,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>CLUNY</t>
+          <t>REPULSE</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Cluny Power Station</t>
+          <t>Repulse Power Station</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -2818,7 +2822,7 @@
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>0.9933</v>
@@ -3436,7 +3440,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>GEORGTN2</t>
+          <t>GEORGTN1</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -3473,12 +3477,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>GEORGTN1</t>
+          <t>MEADOWB2</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>GEORGE TOWN DIESEL</t>
+          <t>Meadowbank Power Station</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
@@ -3486,7 +3490,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr"/>
       <c r="E46" s="5" t="n">
-        <v>1.0092</v>
+        <v>0.9737</v>
       </c>
       <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="5" t="inlineStr"/>
@@ -3510,24 +3514,20 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CATAGUN1</t>
+          <t>GEORGTN2</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>24</v>
-      </c>
+          <t>GEORGE TOWN DIESEL</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D47" s="3" t="inlineStr"/>
       <c r="E47" s="5" t="n">
-        <v>0.9915</v>
+        <v>1.0092</v>
       </c>
       <c r="F47" s="5" t="inlineStr"/>
       <c r="G47" s="5" t="inlineStr"/>
@@ -3551,20 +3551,24 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>MEADOWB2</t>
+          <t>CATAGUN1</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Meadowbank Power Station</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D48" s="3" t="inlineStr"/>
+          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>24</v>
+      </c>
       <c r="E48" s="5" t="n">
-        <v>0.9737</v>
+        <v>0.9915</v>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="5" t="inlineStr"/>
@@ -4935,7 +4939,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE1</t>
+          <t>TVPP104</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
@@ -4981,7 +4985,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE2</t>
+          <t>BBTHREE3</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
@@ -5027,7 +5031,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE3</t>
+          <t>BBTHREE2</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
@@ -5073,7 +5077,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>TVPP104</t>
+          <t>BBTHREE1</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
@@ -5165,11 +5169,11 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>TVCC201</t>
+          <t>DG_TAS1</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="C31" s="5" t="n">
         <v>1</v>
@@ -5178,7 +5182,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="F31" s="5" t="n">
         <v>1</v>
@@ -5211,11 +5215,11 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>DG_TAS1</t>
+          <t>TVCC201</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="C32" s="5" t="n">
         <v>1</v>
@@ -5224,7 +5228,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>1</v>
@@ -5303,7 +5307,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>REPULSE</t>
+          <t>CLUNY</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
@@ -5349,7 +5353,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>CLUNY</t>
+          <t>REPULSE</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
@@ -5779,7 +5783,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>GEORGTN2</t>
+          <t>GEORGTN1</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
@@ -5803,11 +5807,11 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>GEORGTN1</t>
+          <t>MEADOWB2</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1.0092</v>
+        <v>0.9737</v>
       </c>
       <c r="C46" s="5" t="inlineStr"/>
       <c r="D46" s="5" t="inlineStr"/>
@@ -5827,11 +5831,11 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CATAGUN1</t>
+          <t>GEORGTN2</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>0.9915</v>
+        <v>1.0092</v>
       </c>
       <c r="C47" s="5" t="inlineStr"/>
       <c r="D47" s="5" t="inlineStr"/>
@@ -5851,11 +5855,11 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>MEADOWB2</t>
+          <t>CATAGUN1</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>0.9737</v>
+        <v>0.9915</v>
       </c>
       <c r="C48" s="5" t="inlineStr"/>
       <c r="D48" s="5" t="inlineStr"/>
@@ -6208,7 +6212,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE1</t>
+          <t>TVPP104</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -6237,7 +6241,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE2</t>
+          <t>BBTHREE3</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -6266,7 +6270,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE3</t>
+          <t>BBTHREE2</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -6295,7 +6299,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>TVPP104</t>
+          <t>BBTHREE1</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -6332,7 +6336,11 @@
           <t>Basslink HVDC Link</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
       <c r="D7" s="5" t="n">
         <v>1</v>
       </c>
@@ -6349,19 +6357,15 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>TVCC201</t>
+          <t>DG_TAS1</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Tamar Valley Combined Cycle Power Station</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
+          <t>TAS1 Dummy Generator</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="5" t="n">
         <v>1</v>
       </c>
@@ -6378,15 +6382,19 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>DG_TAS1</t>
+          <t>TVCC201</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>TAS1 Dummy Generator</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr"/>
+          <t>Tamar Valley Combined Cycle Power Station</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="n">
         <v>1</v>
       </c>
@@ -7284,12 +7292,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>REPULSE</t>
+          <t>CLUNY</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Repulse Power Station</t>
+          <t>Cluny Power Station</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -7313,12 +7321,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>CLUNY</t>
+          <t>REPULSE</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Cluny Power Station</t>
+          <t>Repulse Power Station</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">

--- a/outputs/TAS_mlf.xlsx
+++ b/outputs/TAS_mlf.xlsx
@@ -2485,13 +2485,9 @@
           <t>Basslink HVDC Link</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
+      <c r="C30" s="3" t="inlineStr"/>
       <c r="D30" s="4" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>1</v>
@@ -6336,11 +6332,7 @@
           <t>Basslink HVDC Link</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
+      <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="5" t="n">
         <v>1</v>
       </c>

--- a/outputs/TAS_mlf.xlsx
+++ b/outputs/TAS_mlf.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2209,7 +2209,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TVPP104</t>
+          <t>BBTHREE1</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>0.9995000000000001</v>
@@ -2276,7 +2276,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE3</t>
+          <t>BBTHREE2</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2343,7 +2343,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE2</t>
+          <t>BBTHREE3</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2410,7 +2410,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE1</t>
+          <t>TVPP104</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>0.9995000000000001</v>
@@ -2485,7 +2485,7 @@
           <t>Basslink HVDC Link</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="n"/>
       <c r="D30" s="4" t="n">
         <v>480</v>
       </c>
@@ -2540,20 +2540,24 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>DG_TAS1</t>
+          <t>TVCC201</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>TAS1 Dummy Generator</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr"/>
+          <t>Tamar Valley Combined Cycle Power Station</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
       <c r="D31" s="4" t="n">
-        <v>3000</v>
+        <v>208.6</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="F31" s="5" t="n">
         <v>1</v>
@@ -2562,7 +2566,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="I31" s="5" t="n">
         <v>1</v>
@@ -2603,24 +2607,20 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TVCC201</t>
+          <t>DG_TAS1</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Tamar Valley Combined Cycle Power Station</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
+          <t>TAS1 Dummy Generator</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n"/>
       <c r="D32" s="4" t="n">
-        <v>208.6</v>
+        <v>3000</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>1</v>
@@ -2629,7 +2629,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>1</v>
@@ -2737,12 +2737,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>CLUNY</t>
+          <t>REPULSE</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Cluny Power Station</t>
+          <t>Repulse Power Station</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E34" s="5" t="n">
         <v>0.9933</v>
@@ -2804,12 +2804,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>REPULSE</t>
+          <t>CLUNY</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Repulse Power Station</t>
+          <t>Cluny Power Station</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>0.9933</v>
@@ -3340,7 +3340,7 @@
           <t>Midlands Power Station</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
+      <c r="C43" s="3" t="n"/>
       <c r="D43" s="4" t="n">
         <v>6</v>
       </c>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E44" s="5" t="n">
         <v>0.9602000000000001</v>
@@ -3436,7 +3436,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>GEORGTN1</t>
+          <t>GEORGTN2</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -3444,10 +3444,14 @@
           <t>GEORGE TOWN DIESEL</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D45" s="3" t="inlineStr"/>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="E45" s="5" t="n">
         <v>1.0092</v>
       </c>
@@ -3473,20 +3477,24 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>MEADOWB2</t>
+          <t>GEORGTN1</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Meadowbank Power Station</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D46" s="3" t="inlineStr"/>
+          <t>GEORGE TOWN DIESEL</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="E46" s="5" t="n">
-        <v>0.9737</v>
+        <v>1.0092</v>
       </c>
       <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="5" t="inlineStr"/>
@@ -3510,20 +3518,24 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>GEORGTN2</t>
+          <t>CATAGUN1</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>GEORGE TOWN DIESEL</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D47" s="3" t="inlineStr"/>
+          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>24</v>
+      </c>
       <c r="E47" s="5" t="n">
-        <v>1.0092</v>
+        <v>0.9915</v>
       </c>
       <c r="F47" s="5" t="inlineStr"/>
       <c r="G47" s="5" t="inlineStr"/>
@@ -3547,12 +3559,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>CATAGUN1</t>
+          <t>MEADOWB2</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
+          <t>Meadowbank Power Station</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -3564,7 +3576,7 @@
         <v>24</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.9915</v>
+        <v>0.9737</v>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="5" t="inlineStr"/>
@@ -3602,7 +3614,7 @@
         </is>
       </c>
       <c r="D49" s="4" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="E49" s="5" t="n">
         <v>0.9099</v>
@@ -4935,7 +4947,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TVPP104</t>
+          <t>BBTHREE1</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
@@ -4981,7 +4993,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE3</t>
+          <t>BBTHREE2</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
@@ -5027,7 +5039,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE2</t>
+          <t>BBTHREE3</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
@@ -5073,7 +5085,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE1</t>
+          <t>TVPP104</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
@@ -5165,11 +5177,11 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>DG_TAS1</t>
+          <t>TVCC201</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="C31" s="5" t="n">
         <v>1</v>
@@ -5178,7 +5190,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="F31" s="5" t="n">
         <v>1</v>
@@ -5211,11 +5223,11 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TVCC201</t>
+          <t>DG_TAS1</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="C32" s="5" t="n">
         <v>1</v>
@@ -5224,7 +5236,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>1</v>
@@ -5303,7 +5315,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>CLUNY</t>
+          <t>REPULSE</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
@@ -5349,7 +5361,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>REPULSE</t>
+          <t>CLUNY</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
@@ -5779,7 +5791,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>GEORGTN1</t>
+          <t>GEORGTN2</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
@@ -5803,11 +5815,11 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>MEADOWB2</t>
+          <t>GEORGTN1</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>0.9737</v>
+        <v>1.0092</v>
       </c>
       <c r="C46" s="5" t="inlineStr"/>
       <c r="D46" s="5" t="inlineStr"/>
@@ -5827,11 +5839,11 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>GEORGTN2</t>
+          <t>CATAGUN1</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1.0092</v>
+        <v>0.9915</v>
       </c>
       <c r="C47" s="5" t="inlineStr"/>
       <c r="D47" s="5" t="inlineStr"/>
@@ -5851,11 +5863,11 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>CATAGUN1</t>
+          <t>MEADOWB2</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>0.9915</v>
+        <v>0.9737</v>
       </c>
       <c r="C48" s="5" t="inlineStr"/>
       <c r="D48" s="5" t="inlineStr"/>
@@ -6079,7 +6091,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L51">
+  <conditionalFormatting sqref="M2:M51">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -6091,44 +6103,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M51">
+  <conditionalFormatting sqref="O2:O51">
     <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N51">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O51">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P51">
-    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6149,7 +6125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6208,7 +6184,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>TVPP104</t>
+          <t>BBTHREE1</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -6237,7 +6213,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE3</t>
+          <t>BBTHREE2</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -6266,7 +6242,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE2</t>
+          <t>BBTHREE3</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -6295,7 +6271,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE1</t>
+          <t>TVPP104</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -6321,152 +6297,88 @@
         <v>-0.09</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>BLNKTAS</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Basslink HVDC Link</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>DG_TAS1</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>TAS1 Dummy Generator</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>TVCC201</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Tamar Valley Combined Cycle Power Station</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>0</v>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>TAS — Most Improved (YoY)</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>BUTLERSG</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Butlers Gorge Power Station</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>0.9475</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>0.9396</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>0.84</v>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>DUID</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Station</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Fuel Type</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>Latest MLF</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Prev MLF</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>YoY Change</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>YoY %</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>MUSSELR1</t>
+          <t>REECE1</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Musselroe Wind Farm</t>
+          <t>Reece Power Station</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.9188</v>
+        <v>0.9493</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.9101</v>
+        <v>0.9203</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.029</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.96</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>POAT110</t>
+          <t>BASTYAN</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Poatina Power Station</t>
+          <t>Bastyan Power Station</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -6475,27 +6387,27 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.9872</v>
+        <v>0.9623</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.0109</v>
+        <v>0.0283</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>1.12</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>TREVALLN</t>
+          <t>MEADOWBK</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Trevallyn Power Station</t>
+          <t>Meadowbank Power Station</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -6504,27 +6416,27 @@
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.997</v>
+        <v>1.0091</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.9852</v>
+        <v>0.9811</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.0118</v>
+        <v>0.028</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1.2</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>POAT220</t>
+          <t>GORDON</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Poatina Power Station</t>
+          <t>Gordon Power Station</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -6533,56 +6445,56 @@
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.9972</v>
+        <v>0.9872</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.9845</v>
+        <v>0.9594</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.0127</v>
+        <v>0.0278</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>1.29</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>GRANWF1</t>
+          <t>TUNGATIN</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Granville Harbour Wind Farm</t>
+          <t>Tungatinah Power Station</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.9688</v>
+        <v>0.9334</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.9555</v>
+        <v>0.9061</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0273</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>1.39</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>DEVILS_G</t>
+          <t>REECE2</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Devils Gate Power Station</t>
+          <t>Reece Power Station</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -6591,27 +6503,27 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.9761</v>
+        <v>0.946</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.9616</v>
+        <v>0.9187</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0273</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>1.51</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>LK_ECHO</t>
+          <t>ROWALLAN</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Lake Echo Power Station</t>
+          <t>Rowallan Power Station</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -6620,85 +6532,81 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.946</v>
+        <v>0.9796</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.9314</v>
+        <v>0.9533</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.0263</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1.57</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>WOOLNTH1</t>
+          <t>FISHER</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Woolnorth Studland Bay / Bluff Point Wind Farm</t>
+          <t>Fisher Power Station</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.9371</v>
+        <v>0.9796</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.9224</v>
+        <v>0.9533</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.0147</v>
+        <v>0.0263</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>1.59</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>PALOONA</t>
+          <t>MIDLDPS1</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Paloona Power Station</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
+          <t>Midlands Power Station</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n"/>
       <c r="D19" s="5" t="n">
-        <v>0.9802999999999999</v>
+        <v>1.0368</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.9648</v>
+        <v>1.0121</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.0155</v>
+        <v>0.0247</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>1.61</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>WYA252B1</t>
+          <t>TRIBUTE</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
+          <t>Tribute Power Station</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -6707,27 +6615,27 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>1.0075</v>
+        <v>0.9505</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.9265</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.0156</v>
+        <v>0.024</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>1.57</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>WYB252B1</t>
+          <t>CETHANA</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
+          <t>Cethana Power Station</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -6736,27 +6644,27 @@
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1.0075</v>
+        <v>0.9705</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.9473</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.0156</v>
+        <v>0.0232</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>L_W_CNL1</t>
+          <t>MACKNTSH</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
+          <t>Mackintosh Power Station</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -6765,71 +6673,143 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>1.0075</v>
+        <v>0.9429</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.9919</v>
+        <v>0.92</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.0156</v>
+        <v>0.0229</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>1.57</v>
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>PO110NL1</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Poatina Power Station</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1.012</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.9891</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.0229</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>GOVILLB1</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Gordon Power Station</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1.0141</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.9918</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.0223</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>TAS — Most Improved (YoY)</t>
-        </is>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>JBUTTERS</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>John Butters Power Station</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0.9602000000000001</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0.9386</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0.0216</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>DUID</t>
-        </is>
-      </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>Station</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>Fuel Type</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>Latest MLF</t>
-        </is>
-      </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>Prev MLF</t>
-        </is>
-      </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>YoY Change</t>
-        </is>
-      </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>YoY %</t>
-        </is>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TRIBNL1</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Tribute Power Station</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>0.9792999999999999</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0.9586</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0.0207</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>2.16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>REECE1</t>
+          <t>REPULSE</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Reece Power Station</t>
+          <t>Repulse Power Station</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -6838,27 +6818,27 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0.9493</v>
+        <v>1.0055</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0.9203</v>
+        <v>0.9857</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.029</v>
+        <v>0.0198</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>3.15</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>BASTYAN</t>
+          <t>CLUNY</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Bastyan Power Station</t>
+          <t>Cluny Power Station</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -6867,27 +6847,27 @@
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>0.9623</v>
+        <v>1.0055</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9857</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.0198</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>3.03</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>MEADOWBK</t>
+          <t>LI_WY_CA</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Meadowbank Power Station</t>
+          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -6896,27 +6876,27 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>1.0091</v>
+        <v>1.0052</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.9811</v>
+        <v>0.9855</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0197</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>2.85</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>GORDON</t>
+          <t>LEM_WIL</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Gordon Power Station</t>
+          <t>Lemonthyme / Wilmot Power Station</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -6925,475 +6905,15 @@
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>0.9872</v>
+        <v>0.9863</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.9594</v>
+        <v>0.9676</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.0278</v>
+        <v>0.0187</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>TUNGATIN</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Tungatinah Power Station</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>0.9334</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>0.9061</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>0.0273</v>
-      </c>
-      <c r="G31" s="6" t="n">
-        <v>3.01</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>REECE2</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Reece Power Station</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>0.946</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>0.9187</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>0.0273</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>2.97</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>ROWALLAN</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Rowallan Power Station</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>0.9796</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>0.9533</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>0.0263</v>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>2.76</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>FISHER</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Fisher Power Station</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>0.9796</v>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>0.9533</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>0.0263</v>
-      </c>
-      <c r="G34" s="6" t="n">
-        <v>2.76</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>MIDLDPS1</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Midlands Power Station</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="5" t="n">
-        <v>1.0368</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>1.0121</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>0.0247</v>
-      </c>
-      <c r="G35" s="6" t="n">
-        <v>2.44</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>TRIBUTE</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Tribute Power Station</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>0.9505</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>0.9265</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="G36" s="6" t="n">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>CETHANA</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Cethana Power Station</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>0.9705</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>0.9473</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>0.0232</v>
-      </c>
-      <c r="G37" s="6" t="n">
-        <v>2.45</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>MACKNTSH</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Mackintosh Power Station</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>0.9429</v>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>0.0229</v>
-      </c>
-      <c r="G38" s="6" t="n">
-        <v>2.49</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>PO110NL1</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Poatina Power Station</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>1.012</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0.9891</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>0.0229</v>
-      </c>
-      <c r="G39" s="6" t="n">
-        <v>2.32</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>GOVILLB1</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Gordon Power Station</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>1.0141</v>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>0.9918</v>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>0.0223</v>
-      </c>
-      <c r="G40" s="6" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>JBUTTERS</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>John Butters Power Station</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>0.9602000000000001</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>0.9386</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>0.0216</v>
-      </c>
-      <c r="G41" s="6" t="n">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>TRIBNL1</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Tribute Power Station</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>0.9792999999999999</v>
-      </c>
-      <c r="E42" s="5" t="n">
-        <v>0.9586</v>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>0.0207</v>
-      </c>
-      <c r="G42" s="6" t="n">
-        <v>2.16</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>CLUNY</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Cluny Power Station</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>1.0055</v>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>0.9857</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>0.0198</v>
-      </c>
-      <c r="G43" s="6" t="n">
-        <v>2.01</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>REPULSE</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Repulse Power Station</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>1.0055</v>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>0.9857</v>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>0.0198</v>
-      </c>
-      <c r="G44" s="6" t="n">
-        <v>2.01</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>LI_WY_CA</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>1.0052</v>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>0.9855</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>0.0197</v>
-      </c>
-      <c r="G45" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>LEM_WIL</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Lemonthyme / Wilmot Power Station</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>0.9863</v>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>0.9676</v>
-      </c>
-      <c r="F46" s="5" t="n">
-        <v>0.0187</v>
-      </c>
-      <c r="G46" s="6" t="n">
         <v>1.93</v>
       </c>
     </row>

--- a/outputs/TAS_mlf.xlsx
+++ b/outputs/TAS_mlf.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2209,7 +2209,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE1</t>
+          <t>TVPP104</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>0.9995000000000001</v>
@@ -2276,7 +2276,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE2</t>
+          <t>BBTHREE3</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2343,7 +2343,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE3</t>
+          <t>BBTHREE2</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2410,7 +2410,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>TVPP104</t>
+          <t>BBTHREE1</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>0.9995000000000001</v>
@@ -2485,7 +2485,9 @@
           <t>Basslink HVDC Link</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n"/>
+      <c r="C30" s="3" t="n">
+        <v/>
+      </c>
       <c r="D30" s="4" t="n">
         <v>480</v>
       </c>
@@ -2540,24 +2542,22 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>TVCC201</t>
+          <t>DG_TAS1</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Tamar Valley Combined Cycle Power Station</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
+          <t>TAS1 Dummy Generator</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v/>
       </c>
       <c r="D31" s="4" t="n">
-        <v>208.6</v>
+        <v>3000</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="F31" s="5" t="n">
         <v>1</v>
@@ -2566,7 +2566,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="I31" s="5" t="n">
         <v>1</v>
@@ -2607,20 +2607,24 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>DG_TAS1</t>
+          <t>TVCC201</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>TAS1 Dummy Generator</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="n"/>
+          <t>Tamar Valley Combined Cycle Power Station</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
       <c r="D32" s="4" t="n">
-        <v>3000</v>
+        <v>208.6</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>1</v>
@@ -2629,7 +2633,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>1</v>
@@ -2737,12 +2741,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>REPULSE</t>
+          <t>CLUNY</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Repulse Power Station</t>
+          <t>Cluny Power Station</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -2751,7 +2755,7 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E34" s="5" t="n">
         <v>0.9933</v>
@@ -2804,12 +2808,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>CLUNY</t>
+          <t>REPULSE</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Cluny Power Station</t>
+          <t>Repulse Power Station</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -2818,7 +2822,7 @@
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>0.9933</v>
@@ -3340,7 +3344,9 @@
           <t>Midlands Power Station</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n"/>
+      <c r="C43" s="3" t="n">
+        <v/>
+      </c>
       <c r="D43" s="4" t="n">
         <v>6</v>
       </c>
@@ -3436,7 +3442,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>GEORGTN2</t>
+          <t>GEORGTN1</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -3477,12 +3483,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>GEORGTN1</t>
+          <t>MEADOWB2</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>GEORGE TOWN DIESEL</t>
+          <t>Meadowbank Power Station</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -3491,10 +3497,10 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1.0092</v>
+        <v>0.9737</v>
       </c>
       <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="5" t="inlineStr"/>
@@ -3518,12 +3524,12 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CATAGUN1</t>
+          <t>GEORGTN2</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
+          <t>GEORGE TOWN DIESEL</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -3532,10 +3538,10 @@
         </is>
       </c>
       <c r="D47" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0.9915</v>
+        <v>1.0092</v>
       </c>
       <c r="F47" s="5" t="inlineStr"/>
       <c r="G47" s="5" t="inlineStr"/>
@@ -3559,12 +3565,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>MEADOWB2</t>
+          <t>CATAGUN1</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Meadowbank Power Station</t>
+          <t>Catagunya / Liapootah / Wayatinah Power Station</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -3576,7 +3582,7 @@
         <v>24</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.9737</v>
+        <v>0.9915</v>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="5" t="inlineStr"/>
@@ -4947,7 +4953,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE1</t>
+          <t>TVPP104</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
@@ -4993,7 +4999,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE2</t>
+          <t>BBTHREE3</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
@@ -5039,7 +5045,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE3</t>
+          <t>BBTHREE2</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
@@ -5085,7 +5091,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>TVPP104</t>
+          <t>BBTHREE1</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
@@ -5177,11 +5183,11 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>TVCC201</t>
+          <t>DG_TAS1</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="C31" s="5" t="n">
         <v>1</v>
@@ -5190,7 +5196,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="F31" s="5" t="n">
         <v>1</v>
@@ -5223,11 +5229,11 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>DG_TAS1</t>
+          <t>TVCC201</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="C32" s="5" t="n">
         <v>1</v>
@@ -5236,7 +5242,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>1</v>
@@ -5315,7 +5321,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>REPULSE</t>
+          <t>CLUNY</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
@@ -5361,7 +5367,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>CLUNY</t>
+          <t>REPULSE</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
@@ -5791,7 +5797,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>GEORGTN2</t>
+          <t>GEORGTN1</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
@@ -5815,11 +5821,11 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>GEORGTN1</t>
+          <t>MEADOWB2</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1.0092</v>
+        <v>0.9737</v>
       </c>
       <c r="C46" s="5" t="inlineStr"/>
       <c r="D46" s="5" t="inlineStr"/>
@@ -5839,11 +5845,11 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CATAGUN1</t>
+          <t>GEORGTN2</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>0.9915</v>
+        <v>1.0092</v>
       </c>
       <c r="C47" s="5" t="inlineStr"/>
       <c r="D47" s="5" t="inlineStr"/>
@@ -5863,11 +5869,11 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>MEADOWB2</t>
+          <t>CATAGUN1</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>0.9737</v>
+        <v>0.9915</v>
       </c>
       <c r="C48" s="5" t="inlineStr"/>
       <c r="D48" s="5" t="inlineStr"/>
@@ -6184,7 +6190,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE1</t>
+          <t>TVPP104</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -6213,7 +6219,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE2</t>
+          <t>BBTHREE3</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -6242,7 +6248,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BBTHREE3</t>
+          <t>BBTHREE2</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -6271,7 +6277,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>TVPP104</t>
+          <t>BBTHREE1</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -6584,7 +6590,9 @@
           <t>Midlands Power Station</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
+      <c r="C19" s="3" t="n">
+        <v/>
+      </c>
       <c r="D19" s="5" t="n">
         <v>1.0368</v>
       </c>
@@ -6804,12 +6812,12 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>REPULSE</t>
+          <t>CLUNY</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Repulse Power Station</t>
+          <t>Cluny Power Station</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -6833,12 +6841,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>CLUNY</t>
+          <t>REPULSE</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Cluny Power Station</t>
+          <t>Repulse Power Station</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
